--- a/prueba_envio_dos_certificados.xlsx
+++ b/prueba_envio_dos_certificados.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Certificado Oficial de Asistencia y Grabación - II Foro de Editores de Revistas Científicas 2026</t>
+          <t>Certificado Oficial de Asistencia - II Foro de Editores de Revistas Científicas 2026</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Certificado Oficial de Ponente y Grabación - II Foro de Editores de Revistas Científicas 2026</t>
+          <t>Certificado Oficial de Ponente - II Foro de Editores de Revistas Científicas 2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
